--- a/data/extracted/inventory-receipts/REP CONTENEDOR P200.XLSX
+++ b/data/extracted/inventory-receipts/REP CONTENEDOR P200.XLSX
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AF0036-DESKTOP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\txpacifico\txp-inventory\data\extracted\inventory-receipts\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE649CEE-E54C-4168-952F-C48848CB3064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10080" windowHeight="9465"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="IBUM" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -2573,7 +2586,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="###,###,###,###,##0.#0"/>
   </numFmts>
@@ -2614,12 +2627,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2899,50 +2911,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L618"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="1" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -2980,12 +2992,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -3023,7 +3035,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -3061,7 +3073,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -3099,7 +3111,7 @@
         <v>19.45</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -3137,7 +3149,7 @@
         <v>18.25</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -3175,7 +3187,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -3213,7 +3225,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -3251,7 +3263,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -3289,7 +3301,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -3327,7 +3339,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -3365,7 +3377,7 @@
         <v>19.55</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -3403,7 +3415,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -3441,7 +3453,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -3479,7 +3491,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -3517,7 +3529,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -3555,7 +3567,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -3593,7 +3605,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -3631,7 +3643,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -3669,7 +3681,7 @@
         <v>19.649999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -3707,7 +3719,7 @@
         <v>19.45</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -3745,7 +3757,7 @@
         <v>19.149999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -3783,7 +3795,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -3821,7 +3833,7 @@
         <v>19.95</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -3859,7 +3871,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F30" s="1" t="s">
         <v>81</v>
       </c>
@@ -3879,7 +3891,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F31" s="1" t="s">
         <v>79</v>
       </c>
@@ -3899,7 +3911,7 @@
         <v>447.39999999999992</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -3937,7 +3949,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -3975,7 +3987,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -4013,7 +4025,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -4051,7 +4063,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -4089,7 +4101,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -4127,7 +4139,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -4165,7 +4177,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -4203,7 +4215,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -4241,7 +4253,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
@@ -4279,7 +4291,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -4317,7 +4329,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -4355,7 +4367,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -4393,7 +4405,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -4431,7 +4443,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -4469,7 +4481,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -4507,7 +4519,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -4545,7 +4557,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
@@ -4583,7 +4595,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
@@ -4621,7 +4633,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -4659,7 +4671,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -4697,7 +4709,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -4735,7 +4747,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
@@ -4773,7 +4785,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
@@ -4811,7 +4823,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -4849,7 +4861,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -4887,7 +4899,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -4925,7 +4937,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>19</v>
       </c>
@@ -4963,7 +4975,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -5001,7 +5013,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -5039,7 +5051,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -5077,7 +5089,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>19</v>
       </c>
@@ -5115,7 +5127,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5153,7 +5165,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>19</v>
       </c>
@@ -5191,7 +5203,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>19</v>
       </c>
@@ -5229,7 +5241,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>19</v>
       </c>
@@ -5267,7 +5279,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>19</v>
       </c>
@@ -5305,7 +5317,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -5343,7 +5355,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>19</v>
       </c>
@@ -5381,7 +5393,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -5419,7 +5431,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>19</v>
       </c>
@@ -5457,7 +5469,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -5495,7 +5507,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>19</v>
       </c>
@@ -5533,7 +5545,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>19</v>
       </c>
@@ -5571,7 +5583,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>19</v>
       </c>
@@ -5609,7 +5621,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -5647,7 +5659,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F78" s="1" t="s">
         <v>81</v>
       </c>
@@ -5667,7 +5679,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F79" s="1" t="s">
         <v>114</v>
       </c>
@@ -5687,7 +5699,7 @@
         <v>929.1000000000007</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>19</v>
       </c>
@@ -5725,7 +5737,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
@@ -5763,7 +5775,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>19</v>
       </c>
@@ -5801,7 +5813,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -5839,7 +5851,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>19</v>
       </c>
@@ -5877,7 +5889,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>19</v>
       </c>
@@ -5915,7 +5927,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>19</v>
       </c>
@@ -5953,7 +5965,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>19</v>
       </c>
@@ -5991,7 +6003,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>19</v>
       </c>
@@ -6029,7 +6041,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -6067,7 +6079,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>19</v>
       </c>
@@ -6105,7 +6117,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>19</v>
       </c>
@@ -6143,7 +6155,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
@@ -6181,7 +6193,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>19</v>
       </c>
@@ -6219,7 +6231,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>19</v>
       </c>
@@ -6257,7 +6269,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>19</v>
       </c>
@@ -6295,7 +6307,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>19</v>
       </c>
@@ -6333,7 +6345,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>19</v>
       </c>
@@ -6371,7 +6383,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>19</v>
       </c>
@@ -6409,7 +6421,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>19</v>
       </c>
@@ -6447,7 +6459,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>19</v>
       </c>
@@ -6485,7 +6497,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>19</v>
       </c>
@@ -6523,7 +6535,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>19</v>
       </c>
@@ -6561,7 +6573,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>19</v>
       </c>
@@ -6599,7 +6611,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>19</v>
       </c>
@@ -6637,7 +6649,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>19</v>
       </c>
@@ -6675,7 +6687,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>19</v>
       </c>
@@ -6713,7 +6725,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>19</v>
       </c>
@@ -6751,7 +6763,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>19</v>
       </c>
@@ -6789,7 +6801,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>19</v>
       </c>
@@ -6827,7 +6839,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>19</v>
       </c>
@@ -6865,7 +6877,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>19</v>
       </c>
@@ -6903,7 +6915,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>19</v>
       </c>
@@ -6941,7 +6953,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>19</v>
       </c>
@@ -6979,7 +6991,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>19</v>
       </c>
@@ -7017,7 +7029,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>19</v>
       </c>
@@ -7055,7 +7067,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>19</v>
       </c>
@@ -7093,7 +7105,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>19</v>
       </c>
@@ -7131,7 +7143,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>19</v>
       </c>
@@ -7169,7 +7181,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>19</v>
       </c>
@@ -7207,7 +7219,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>19</v>
       </c>
@@ -7245,7 +7257,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>19</v>
       </c>
@@ -7283,7 +7295,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>19</v>
       </c>
@@ -7321,7 +7333,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>19</v>
       </c>
@@ -7359,7 +7371,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>19</v>
       </c>
@@ -7397,7 +7409,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>19</v>
       </c>
@@ -7435,7 +7447,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>19</v>
       </c>
@@ -7473,7 +7485,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>19</v>
       </c>
@@ -7511,7 +7523,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>19</v>
       </c>
@@ -7549,7 +7561,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>19</v>
       </c>
@@ -7587,7 +7599,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>19</v>
       </c>
@@ -7625,7 +7637,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>19</v>
       </c>
@@ -7663,7 +7675,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>19</v>
       </c>
@@ -7701,7 +7713,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>19</v>
       </c>
@@ -7739,7 +7751,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>19</v>
       </c>
@@ -7777,7 +7789,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>19</v>
       </c>
@@ -7815,7 +7827,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>19</v>
       </c>
@@ -7853,7 +7865,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>19</v>
       </c>
@@ -7891,7 +7903,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>19</v>
       </c>
@@ -7929,7 +7941,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>19</v>
       </c>
@@ -7967,7 +7979,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>19</v>
       </c>
@@ -8005,7 +8017,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>19</v>
       </c>
@@ -8043,7 +8055,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>19</v>
       </c>
@@ -8081,7 +8093,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>19</v>
       </c>
@@ -8119,7 +8131,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>19</v>
       </c>
@@ -8157,7 +8169,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>19</v>
       </c>
@@ -8195,7 +8207,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>19</v>
       </c>
@@ -8233,7 +8245,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>19</v>
       </c>
@@ -8271,7 +8283,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>19</v>
       </c>
@@ -8309,7 +8321,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>19</v>
       </c>
@@ -8347,7 +8359,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>19</v>
       </c>
@@ -8385,7 +8397,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>19</v>
       </c>
@@ -8423,7 +8435,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>19</v>
       </c>
@@ -8461,7 +8473,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>19</v>
       </c>
@@ -8499,7 +8511,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>19</v>
       </c>
@@ -8537,7 +8549,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>19</v>
       </c>
@@ -8575,7 +8587,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>19</v>
       </c>
@@ -8613,7 +8625,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>19</v>
       </c>
@@ -8651,7 +8663,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>19</v>
       </c>
@@ -8689,7 +8701,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>19</v>
       </c>
@@ -8727,7 +8739,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>19</v>
       </c>
@@ -8765,7 +8777,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>19</v>
       </c>
@@ -8803,7 +8815,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>19</v>
       </c>
@@ -8841,7 +8853,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>19</v>
       </c>
@@ -8879,7 +8891,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>19</v>
       </c>
@@ -8917,7 +8929,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>19</v>
       </c>
@@ -8955,7 +8967,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>19</v>
       </c>
@@ -8993,7 +9005,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>19</v>
       </c>
@@ -9031,7 +9043,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>19</v>
       </c>
@@ -9069,7 +9081,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>19</v>
       </c>
@@ -9107,7 +9119,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>19</v>
       </c>
@@ -9145,7 +9157,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>19</v>
       </c>
@@ -9183,7 +9195,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>19</v>
       </c>
@@ -9221,7 +9233,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>19</v>
       </c>
@@ -9259,7 +9271,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>19</v>
       </c>
@@ -9297,7 +9309,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>19</v>
       </c>
@@ -9335,7 +9347,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>19</v>
       </c>
@@ -9373,7 +9385,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>19</v>
       </c>
@@ -9411,7 +9423,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>19</v>
       </c>
@@ -9449,7 +9461,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>19</v>
       </c>
@@ -9487,7 +9499,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
         <v>19</v>
       </c>
@@ -9525,7 +9537,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
         <v>19</v>
       </c>
@@ -9563,7 +9575,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>19</v>
       </c>
@@ -9601,7 +9613,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
         <v>19</v>
       </c>
@@ -9639,7 +9651,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
         <v>19</v>
       </c>
@@ -9677,7 +9689,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>19</v>
       </c>
@@ -9715,7 +9727,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
         <v>19</v>
       </c>
@@ -9753,7 +9765,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>19</v>
       </c>
@@ -9791,7 +9803,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>19</v>
       </c>
@@ -9829,7 +9841,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
         <v>19</v>
       </c>
@@ -9867,7 +9879,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>19</v>
       </c>
@@ -9905,7 +9917,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
         <v>19</v>
       </c>
@@ -9943,7 +9955,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>19</v>
       </c>
@@ -9981,7 +9993,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
         <v>19</v>
       </c>
@@ -10019,7 +10031,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>19</v>
       </c>
@@ -10057,7 +10069,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
         <v>19</v>
       </c>
@@ -10095,7 +10107,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>19</v>
       </c>
@@ -10133,7 +10145,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
         <v>19</v>
       </c>
@@ -10171,7 +10183,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
         <v>19</v>
       </c>
@@ -10209,7 +10221,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>19</v>
       </c>
@@ -10247,7 +10259,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>19</v>
       </c>
@@ -10285,7 +10297,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>19</v>
       </c>
@@ -10323,7 +10335,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>19</v>
       </c>
@@ -10361,7 +10373,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
         <v>19</v>
       </c>
@@ -10399,7 +10411,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>19</v>
       </c>
@@ -10437,7 +10449,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
         <v>19</v>
       </c>
@@ -10475,7 +10487,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
         <v>19</v>
       </c>
@@ -10513,7 +10525,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
         <v>19</v>
       </c>
@@ -10551,7 +10563,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
         <v>19</v>
       </c>
@@ -10589,7 +10601,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>19</v>
       </c>
@@ -10627,7 +10639,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>19</v>
       </c>
@@ -10665,7 +10677,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>19</v>
       </c>
@@ -10703,7 +10715,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>19</v>
       </c>
@@ -10741,7 +10753,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>19</v>
       </c>
@@ -10779,7 +10791,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>19</v>
       </c>
@@ -10817,7 +10829,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>19</v>
       </c>
@@ -10855,7 +10867,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>19</v>
       </c>
@@ -10893,7 +10905,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>19</v>
       </c>
@@ -10931,7 +10943,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>19</v>
       </c>
@@ -10969,7 +10981,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>19</v>
       </c>
@@ -11007,7 +11019,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
         <v>19</v>
       </c>
@@ -11045,7 +11057,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>19</v>
       </c>
@@ -11083,7 +11095,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>19</v>
       </c>
@@ -11121,7 +11133,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>19</v>
       </c>
@@ -11159,7 +11171,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>19</v>
       </c>
@@ -11197,7 +11209,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
         <v>19</v>
       </c>
@@ -11235,7 +11247,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
         <v>19</v>
       </c>
@@ -11273,7 +11285,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
         <v>19</v>
       </c>
@@ -11311,7 +11323,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
         <v>19</v>
       </c>
@@ -11349,7 +11361,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
         <v>19</v>
       </c>
@@ -11387,7 +11399,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
         <v>19</v>
       </c>
@@ -11425,7 +11437,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
         <v>19</v>
       </c>
@@ -11463,7 +11475,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
         <v>19</v>
       </c>
@@ -11501,7 +11513,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>19</v>
       </c>
@@ -11539,7 +11551,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
         <v>19</v>
       </c>
@@ -11577,7 +11589,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
         <v>19</v>
       </c>
@@ -11615,7 +11627,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
         <v>19</v>
       </c>
@@ -11653,7 +11665,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
         <v>19</v>
       </c>
@@ -11691,7 +11703,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
         <v>19</v>
       </c>
@@ -11729,7 +11741,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F239" s="1" t="s">
         <v>81</v>
       </c>
@@ -11749,7 +11761,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F240" s="1" t="s">
         <v>428</v>
       </c>
@@ -11766,7 +11778,7 @@
         <v>3185.399999999991</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
         <v>19</v>
       </c>
@@ -11804,7 +11816,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>19</v>
       </c>
@@ -11842,7 +11854,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
         <v>19</v>
       </c>
@@ -11880,7 +11892,7 @@
         <v>18.3</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
         <v>19</v>
       </c>
@@ -11918,7 +11930,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
         <v>19</v>
       </c>
@@ -11956,7 +11968,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
         <v>19</v>
       </c>
@@ -11994,7 +12006,7 @@
         <v>19.05</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>19</v>
       </c>
@@ -12032,7 +12044,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
         <v>19</v>
       </c>
@@ -12070,7 +12082,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>19</v>
       </c>
@@ -12108,7 +12120,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
         <v>19</v>
       </c>
@@ -12146,7 +12158,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
         <v>19</v>
       </c>
@@ -12184,7 +12196,7 @@
         <v>17.05</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
         <v>19</v>
       </c>
@@ -12222,7 +12234,7 @@
         <v>19.55</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
         <v>19</v>
       </c>
@@ -12260,7 +12272,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
         <v>19</v>
       </c>
@@ -12298,7 +12310,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
         <v>19</v>
       </c>
@@ -12336,7 +12348,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
         <v>19</v>
       </c>
@@ -12374,7 +12386,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
         <v>19</v>
       </c>
@@ -12412,7 +12424,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
         <v>19</v>
       </c>
@@ -12450,7 +12462,7 @@
         <v>19.95</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
         <v>19</v>
       </c>
@@ -12488,7 +12500,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
         <v>19</v>
       </c>
@@ -12526,7 +12538,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
         <v>19</v>
       </c>
@@ -12564,7 +12576,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>19</v>
       </c>
@@ -12602,7 +12614,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>19</v>
       </c>
@@ -12640,7 +12652,7 @@
         <v>20.149999999999999</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
         <v>19</v>
       </c>
@@ -12678,7 +12690,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
         <v>19</v>
       </c>
@@ -12716,7 +12728,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
         <v>19</v>
       </c>
@@ -12754,7 +12766,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
         <v>19</v>
       </c>
@@ -12792,7 +12804,7 @@
         <v>19.45</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>19</v>
       </c>
@@ -12830,7 +12842,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>19</v>
       </c>
@@ -12868,7 +12880,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
         <v>19</v>
       </c>
@@ -12906,7 +12918,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>19</v>
       </c>
@@ -12944,7 +12956,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>19</v>
       </c>
@@ -12982,7 +12994,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>19</v>
       </c>
@@ -13020,7 +13032,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
         <v>19</v>
       </c>
@@ -13058,7 +13070,7 @@
         <v>19.55</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
         <v>19</v>
       </c>
@@ -13096,7 +13108,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>19</v>
       </c>
@@ -13134,7 +13146,7 @@
         <v>19.649999999999999</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
         <v>19</v>
       </c>
@@ -13172,7 +13184,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
         <v>19</v>
       </c>
@@ -13210,7 +13222,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
         <v>19</v>
       </c>
@@ -13248,7 +13260,7 @@
         <v>20.149999999999999</v>
       </c>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>19</v>
       </c>
@@ -13286,7 +13298,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
         <v>19</v>
       </c>
@@ -13324,7 +13336,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
         <v>19</v>
       </c>
@@ -13362,7 +13374,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
         <v>19</v>
       </c>
@@ -13400,7 +13412,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>19</v>
       </c>
@@ -13438,7 +13450,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>19</v>
       </c>
@@ -13476,7 +13488,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>19</v>
       </c>
@@ -13514,7 +13526,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>19</v>
       </c>
@@ -13552,7 +13564,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
         <v>19</v>
       </c>
@@ -13590,7 +13602,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
         <v>19</v>
       </c>
@@ -13628,7 +13640,7 @@
         <v>19.149999999999999</v>
       </c>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>19</v>
       </c>
@@ -13666,7 +13678,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>19</v>
       </c>
@@ -13704,7 +13716,7 @@
         <v>19.45</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>19</v>
       </c>
@@ -13742,7 +13754,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
         <v>19</v>
       </c>
@@ -13780,7 +13792,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>19</v>
       </c>
@@ -13818,7 +13830,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>19</v>
       </c>
@@ -13856,7 +13868,7 @@
         <v>18.75</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>19</v>
       </c>
@@ -13894,7 +13906,7 @@
         <v>19.55</v>
       </c>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
         <v>19</v>
       </c>
@@ -13932,7 +13944,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>19</v>
       </c>
@@ -13970,7 +13982,7 @@
         <v>19.55</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>19</v>
       </c>
@@ -14008,7 +14020,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>19</v>
       </c>
@@ -14046,7 +14058,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" s="1" t="s">
         <v>19</v>
       </c>
@@ -14084,7 +14096,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>19</v>
       </c>
@@ -14122,7 +14134,7 @@
         <v>19.649999999999999</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>19</v>
       </c>
@@ -14160,7 +14172,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
         <v>19</v>
       </c>
@@ -14198,7 +14210,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>19</v>
       </c>
@@ -14236,7 +14248,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>19</v>
       </c>
@@ -14274,7 +14286,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="1" t="s">
         <v>19</v>
       </c>
@@ -14312,7 +14324,7 @@
         <v>19.45</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>19</v>
       </c>
@@ -14350,7 +14362,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F309" s="1" t="s">
         <v>81</v>
       </c>
@@ -14370,7 +14382,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F310" s="1" t="s">
         <v>41</v>
       </c>
@@ -14387,7 +14399,7 @@
         <v>1333.3999999999996</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>19</v>
       </c>
@@ -14425,7 +14437,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>19</v>
       </c>
@@ -14463,7 +14475,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>19</v>
       </c>
@@ -14501,7 +14513,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
         <v>19</v>
       </c>
@@ -14539,7 +14551,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>19</v>
       </c>
@@ -14577,7 +14589,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>19</v>
       </c>
@@ -14615,7 +14627,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
         <v>19</v>
       </c>
@@ -14653,7 +14665,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
         <v>19</v>
       </c>
@@ -14691,7 +14703,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>19</v>
       </c>
@@ -14729,7 +14741,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>19</v>
       </c>
@@ -14767,7 +14779,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>19</v>
       </c>
@@ -14805,7 +14817,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>19</v>
       </c>
@@ -14843,7 +14855,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
         <v>19</v>
       </c>
@@ -14881,7 +14893,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
         <v>19</v>
       </c>
@@ -14919,7 +14931,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
         <v>19</v>
       </c>
@@ -14957,7 +14969,7 @@
         <v>20.149999999999999</v>
       </c>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
         <v>19</v>
       </c>
@@ -14995,7 +15007,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
         <v>19</v>
       </c>
@@ -15033,7 +15045,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
         <v>19</v>
       </c>
@@ -15071,7 +15083,7 @@
         <v>20.25</v>
       </c>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>19</v>
       </c>
@@ -15109,7 +15121,7 @@
         <v>20.350000000000001</v>
       </c>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
         <v>19</v>
       </c>
@@ -15147,7 +15159,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>19</v>
       </c>
@@ -15185,7 +15197,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
         <v>19</v>
       </c>
@@ -15223,7 +15235,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>19</v>
       </c>
@@ -15261,7 +15273,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>19</v>
       </c>
@@ -15299,7 +15311,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>19</v>
       </c>
@@ -15337,7 +15349,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
         <v>19</v>
       </c>
@@ -15375,7 +15387,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>19</v>
       </c>
@@ -15413,7 +15425,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>19</v>
       </c>
@@ -15451,7 +15463,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>19</v>
       </c>
@@ -15489,7 +15501,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>19</v>
       </c>
@@ -15527,7 +15539,7 @@
         <v>21.35</v>
       </c>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>19</v>
       </c>
@@ -15565,7 +15577,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>19</v>
       </c>
@@ -15603,7 +15615,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>19</v>
       </c>
@@ -15641,7 +15653,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>19</v>
       </c>
@@ -15679,7 +15691,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>19</v>
       </c>
@@ -15717,7 +15729,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>19</v>
       </c>
@@ -15755,7 +15767,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>19</v>
       </c>
@@ -15793,7 +15805,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>19</v>
       </c>
@@ -15831,7 +15843,7 @@
         <v>20.25</v>
       </c>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>19</v>
       </c>
@@ -15869,7 +15881,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>19</v>
       </c>
@@ -15907,7 +15919,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>19</v>
       </c>
@@ -15945,7 +15957,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>19</v>
       </c>
@@ -15983,7 +15995,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>19</v>
       </c>
@@ -16021,7 +16033,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>19</v>
       </c>
@@ -16059,7 +16071,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" s="1" t="s">
         <v>19</v>
       </c>
@@ -16097,7 +16109,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
         <v>19</v>
       </c>
@@ -16135,7 +16147,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" s="1" t="s">
         <v>19</v>
       </c>
@@ -16173,7 +16185,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>19</v>
       </c>
@@ -16211,7 +16223,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>19</v>
       </c>
@@ -16249,7 +16261,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>19</v>
       </c>
@@ -16287,7 +16299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" s="1" t="s">
         <v>19</v>
       </c>
@@ -16325,7 +16337,7 @@
         <v>19.350000000000001</v>
       </c>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>19</v>
       </c>
@@ -16363,7 +16375,7 @@
         <v>19.95</v>
       </c>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" s="1" t="s">
         <v>19</v>
       </c>
@@ -16401,7 +16413,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
         <v>19</v>
       </c>
@@ -16439,7 +16451,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" s="1" t="s">
         <v>19</v>
       </c>
@@ -16477,7 +16489,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>19</v>
       </c>
@@ -16515,7 +16527,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>19</v>
       </c>
@@ -16553,7 +16565,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>19</v>
       </c>
@@ -16591,7 +16603,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A369" s="1" t="s">
         <v>19</v>
       </c>
@@ -16629,7 +16641,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
         <v>19</v>
       </c>
@@ -16667,7 +16679,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>19</v>
       </c>
@@ -16705,7 +16717,7 @@
         <v>20.350000000000001</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>19</v>
       </c>
@@ -16743,7 +16755,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>19</v>
       </c>
@@ -16781,7 +16793,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
         <v>19</v>
       </c>
@@ -16819,7 +16831,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A375" s="1" t="s">
         <v>19</v>
       </c>
@@ -16857,7 +16869,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
         <v>19</v>
       </c>
@@ -16895,7 +16907,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A377" s="1" t="s">
         <v>19</v>
       </c>
@@ -16933,7 +16945,7 @@
         <v>20.45</v>
       </c>
     </row>
-    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
         <v>19</v>
       </c>
@@ -16971,7 +16983,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" s="1" t="s">
         <v>19</v>
       </c>
@@ -17009,7 +17021,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
         <v>19</v>
       </c>
@@ -17047,7 +17059,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
         <v>19</v>
       </c>
@@ -17085,7 +17097,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
         <v>19</v>
       </c>
@@ -17123,7 +17135,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A383" s="1" t="s">
         <v>19</v>
       </c>
@@ -17161,7 +17173,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
         <v>19</v>
       </c>
@@ -17199,7 +17211,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>19</v>
       </c>
@@ -17237,7 +17249,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>19</v>
       </c>
@@ -17275,7 +17287,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>19</v>
       </c>
@@ -17313,7 +17325,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>19</v>
       </c>
@@ -17351,7 +17363,7 @@
         <v>28.85</v>
       </c>
     </row>
-    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>19</v>
       </c>
@@ -17389,7 +17401,7 @@
         <v>20.350000000000001</v>
       </c>
     </row>
-    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>19</v>
       </c>
@@ -17427,7 +17439,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>19</v>
       </c>
@@ -17465,7 +17477,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>19</v>
       </c>
@@ -17503,7 +17515,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>19</v>
       </c>
@@ -17541,7 +17553,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>19</v>
       </c>
@@ -17579,7 +17591,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>19</v>
       </c>
@@ -17617,7 +17629,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>19</v>
       </c>
@@ -17655,7 +17667,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>19</v>
       </c>
@@ -17693,7 +17705,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>19</v>
       </c>
@@ -17731,7 +17743,7 @@
         <v>21.85</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>19</v>
       </c>
@@ -17769,7 +17781,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>19</v>
       </c>
@@ -17807,7 +17819,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A401" s="1" t="s">
         <v>19</v>
       </c>
@@ -17845,7 +17857,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
         <v>19</v>
       </c>
@@ -17883,7 +17895,7 @@
         <v>21.35</v>
       </c>
     </row>
-    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A403" s="1" t="s">
         <v>19</v>
       </c>
@@ -17921,7 +17933,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
         <v>19</v>
       </c>
@@ -17959,7 +17971,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405" s="1" t="s">
         <v>19</v>
       </c>
@@ -17997,7 +18009,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
         <v>19</v>
       </c>
@@ -18035,7 +18047,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A407" s="1" t="s">
         <v>19</v>
       </c>
@@ -18073,7 +18085,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
         <v>19</v>
       </c>
@@ -18111,7 +18123,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A409" s="1" t="s">
         <v>19</v>
       </c>
@@ -18149,7 +18161,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
         <v>19</v>
       </c>
@@ -18187,7 +18199,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411" s="1" t="s">
         <v>19</v>
       </c>
@@ -18225,7 +18237,7 @@
         <v>20.25</v>
       </c>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>19</v>
       </c>
@@ -18263,7 +18275,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>19</v>
       </c>
@@ -18301,7 +18313,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
         <v>19</v>
       </c>
@@ -18339,7 +18351,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A415" s="1" t="s">
         <v>19</v>
       </c>
@@ -18377,7 +18389,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
         <v>19</v>
       </c>
@@ -18415,7 +18427,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>19</v>
       </c>
@@ -18453,7 +18465,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>19</v>
       </c>
@@ -18491,7 +18503,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A419" s="1" t="s">
         <v>19</v>
       </c>
@@ -18529,7 +18541,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>19</v>
       </c>
@@ -18567,7 +18579,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>19</v>
       </c>
@@ -18605,7 +18617,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>19</v>
       </c>
@@ -18643,7 +18655,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423" s="1" t="s">
         <v>19</v>
       </c>
@@ -18681,7 +18693,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
         <v>19</v>
       </c>
@@ -18719,7 +18731,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A425" s="1" t="s">
         <v>19</v>
       </c>
@@ -18757,7 +18769,7 @@
         <v>19.95</v>
       </c>
     </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
         <v>19</v>
       </c>
@@ -18795,7 +18807,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A427" s="1" t="s">
         <v>19</v>
       </c>
@@ -18833,7 +18845,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>19</v>
       </c>
@@ -18871,7 +18883,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>19</v>
       </c>
@@ -18909,7 +18921,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
         <v>19</v>
       </c>
@@ -18947,7 +18959,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>19</v>
       </c>
@@ -18985,7 +18997,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>19</v>
       </c>
@@ -19023,7 +19035,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A433" s="1" t="s">
         <v>19</v>
       </c>
@@ -19061,7 +19073,7 @@
         <v>20.350000000000001</v>
       </c>
     </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
         <v>19</v>
       </c>
@@ -19099,7 +19111,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
         <v>19</v>
       </c>
@@ -19137,7 +19149,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
         <v>19</v>
       </c>
@@ -19175,7 +19187,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A437" s="1" t="s">
         <v>19</v>
       </c>
@@ -19213,7 +19225,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
         <v>19</v>
       </c>
@@ -19251,7 +19263,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A439" s="1" t="s">
         <v>19</v>
       </c>
@@ -19289,7 +19301,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
         <v>19</v>
       </c>
@@ -19327,7 +19339,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
         <v>19</v>
       </c>
@@ -19365,7 +19377,7 @@
         <v>21.35</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
         <v>19</v>
       </c>
@@ -19403,7 +19415,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
         <v>19</v>
       </c>
@@ -19441,7 +19453,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
         <v>19</v>
       </c>
@@ -19479,7 +19491,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A445" s="1" t="s">
         <v>19</v>
       </c>
@@ -19517,7 +19529,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
         <v>19</v>
       </c>
@@ -19555,7 +19567,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
         <v>19</v>
       </c>
@@ -19593,7 +19605,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
         <v>19</v>
       </c>
@@ -19631,7 +19643,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
         <v>19</v>
       </c>
@@ -19669,7 +19681,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
         <v>19</v>
       </c>
@@ -19707,7 +19719,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A451" s="1" t="s">
         <v>19</v>
       </c>
@@ -19745,7 +19757,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
         <v>19</v>
       </c>
@@ -19783,7 +19795,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
         <v>19</v>
       </c>
@@ -19821,7 +19833,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
         <v>19</v>
       </c>
@@ -19859,7 +19871,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
         <v>19</v>
       </c>
@@ -19897,7 +19909,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
         <v>19</v>
       </c>
@@ -19935,7 +19947,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A457" s="1" t="s">
         <v>19</v>
       </c>
@@ -19973,7 +19985,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
         <v>19</v>
       </c>
@@ -20011,7 +20023,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
         <v>19</v>
       </c>
@@ -20049,7 +20061,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
         <v>19</v>
       </c>
@@ -20087,7 +20099,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A461" s="1" t="s">
         <v>19</v>
       </c>
@@ -20125,7 +20137,7 @@
         <v>20.350000000000001</v>
       </c>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
         <v>19</v>
       </c>
@@ -20163,7 +20175,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A463" s="1" t="s">
         <v>19</v>
       </c>
@@ -20201,7 +20213,7 @@
         <v>19.55</v>
       </c>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
         <v>19</v>
       </c>
@@ -20239,7 +20251,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A465" s="1" t="s">
         <v>19</v>
       </c>
@@ -20277,7 +20289,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
         <v>19</v>
       </c>
@@ -20315,7 +20327,7 @@
         <v>21.15</v>
       </c>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
         <v>19</v>
       </c>
@@ -20353,7 +20365,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
         <v>19</v>
       </c>
@@ -20391,7 +20403,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
         <v>19</v>
       </c>
@@ -20429,7 +20441,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
         <v>19</v>
       </c>
@@ -20467,7 +20479,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A471" s="1" t="s">
         <v>19</v>
       </c>
@@ -20505,7 +20517,7 @@
         <v>20.45</v>
       </c>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>19</v>
       </c>
@@ -20543,7 +20555,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A473" s="1" t="s">
         <v>19</v>
       </c>
@@ -20581,7 +20593,7 @@
         <v>21.15</v>
       </c>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
         <v>19</v>
       </c>
@@ -20619,7 +20631,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="475" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A475" s="1" t="s">
         <v>19</v>
       </c>
@@ -20657,7 +20669,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
         <v>19</v>
       </c>
@@ -20695,7 +20707,7 @@
         <v>19.05</v>
       </c>
     </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
         <v>19</v>
       </c>
@@ -20733,7 +20745,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
         <v>19</v>
       </c>
@@ -20771,7 +20783,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="479" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A479" s="1" t="s">
         <v>19</v>
       </c>
@@ -20809,7 +20821,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="480" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
         <v>19</v>
       </c>
@@ -20847,7 +20859,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="481" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A481" s="1" t="s">
         <v>19</v>
       </c>
@@ -20885,7 +20897,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
         <v>19</v>
       </c>
@@ -20923,7 +20935,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="483" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A483" s="1" t="s">
         <v>19</v>
       </c>
@@ -20961,7 +20973,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
         <v>19</v>
       </c>
@@ -20999,7 +21011,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="485" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A485" s="1" t="s">
         <v>19</v>
       </c>
@@ -21037,7 +21049,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
         <v>19</v>
       </c>
@@ -21075,7 +21087,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
         <v>19</v>
       </c>
@@ -21113,7 +21125,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="488" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
         <v>19</v>
       </c>
@@ -21151,7 +21163,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="489" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A489" s="1" t="s">
         <v>19</v>
       </c>
@@ -21189,7 +21201,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
         <v>19</v>
       </c>
@@ -21227,7 +21239,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A491" s="1" t="s">
         <v>19</v>
       </c>
@@ -21265,7 +21277,7 @@
         <v>19.7</v>
       </c>
     </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
         <v>19</v>
       </c>
@@ -21303,7 +21315,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="493" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A493" s="1" t="s">
         <v>19</v>
       </c>
@@ -21341,7 +21353,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
         <v>19</v>
       </c>
@@ -21379,7 +21391,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
         <v>19</v>
       </c>
@@ -21417,7 +21429,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
         <v>19</v>
       </c>
@@ -21455,7 +21467,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="497" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A497" s="1" t="s">
         <v>19</v>
       </c>
@@ -21493,7 +21505,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="498" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
         <v>19</v>
       </c>
@@ -21531,7 +21543,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
         <v>19</v>
       </c>
@@ -21569,7 +21581,7 @@
         <v>20.65</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
         <v>19</v>
       </c>
@@ -21607,7 +21619,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="501" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A501" s="1" t="s">
         <v>19</v>
       </c>
@@ -21645,7 +21657,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="502" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
         <v>19</v>
       </c>
@@ -21683,7 +21695,7 @@
         <v>19.95</v>
       </c>
     </row>
-    <row r="503" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A503" s="1" t="s">
         <v>19</v>
       </c>
@@ -21721,7 +21733,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="504" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
         <v>19</v>
       </c>
@@ -21759,7 +21771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="505" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A505" s="1" t="s">
         <v>19</v>
       </c>
@@ -21797,7 +21809,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
         <v>19</v>
       </c>
@@ -21835,7 +21847,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="507" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A507" s="1" t="s">
         <v>19</v>
       </c>
@@ -21873,7 +21885,7 @@
         <v>15.75</v>
       </c>
     </row>
-    <row r="508" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
         <v>19</v>
       </c>
@@ -21911,7 +21923,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
         <v>19</v>
       </c>
@@ -21949,7 +21961,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="510" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
         <v>19</v>
       </c>
@@ -21987,7 +21999,7 @@
         <v>20.95</v>
       </c>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
         <v>19</v>
       </c>
@@ -22025,7 +22037,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
         <v>19</v>
       </c>
@@ -22063,7 +22075,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
         <v>19</v>
       </c>
@@ -22101,7 +22113,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
         <v>19</v>
       </c>
@@ -22139,7 +22151,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="515" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A515" s="1" t="s">
         <v>19</v>
       </c>
@@ -22177,7 +22189,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="516" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
         <v>19</v>
       </c>
@@ -22215,7 +22227,7 @@
         <v>20.45</v>
       </c>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
         <v>19</v>
       </c>
@@ -22253,7 +22265,7 @@
         <v>20.75</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
         <v>19</v>
       </c>
@@ -22291,7 +22303,7 @@
         <v>21.15</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
         <v>19</v>
       </c>
@@ -22329,7 +22341,7 @@
         <v>20.350000000000001</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
         <v>19</v>
       </c>
@@ -22367,7 +22379,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="521" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A521" s="1" t="s">
         <v>19</v>
       </c>
@@ -22405,7 +22417,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="522" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
         <v>19</v>
       </c>
@@ -22443,7 +22455,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="523" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A523" s="1" t="s">
         <v>19</v>
       </c>
@@ -22481,7 +22493,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
         <v>19</v>
       </c>
@@ -22519,7 +22531,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
         <v>19</v>
       </c>
@@ -22557,7 +22569,7 @@
         <v>20.45</v>
       </c>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F526" s="1" t="s">
         <v>81</v>
       </c>
@@ -22577,7 +22589,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F527" s="1" t="s">
         <v>531</v>
       </c>
@@ -22597,7 +22609,7 @@
         <v>4449.0999999999995</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
         <v>19</v>
       </c>
@@ -22635,7 +22647,7 @@
         <v>19.86</v>
       </c>
     </row>
-    <row r="529" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A529" s="1" t="s">
         <v>19</v>
       </c>
@@ -22673,7 +22685,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="530" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
         <v>19</v>
       </c>
@@ -22711,7 +22723,7 @@
         <v>18.87</v>
       </c>
     </row>
-    <row r="531" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A531" s="1" t="s">
         <v>19</v>
       </c>
@@ -22749,7 +22761,7 @@
         <v>20.010000000000002</v>
       </c>
     </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
         <v>19</v>
       </c>
@@ -22787,7 +22799,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A533" s="1" t="s">
         <v>19</v>
       </c>
@@ -22825,7 +22837,7 @@
         <v>19.260000000000002</v>
       </c>
     </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
         <v>19</v>
       </c>
@@ -22863,7 +22875,7 @@
         <v>18.97</v>
       </c>
     </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A535" s="1" t="s">
         <v>19</v>
       </c>
@@ -22901,7 +22913,7 @@
         <v>19.77</v>
       </c>
     </row>
-    <row r="536" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
         <v>19</v>
       </c>
@@ -22939,7 +22951,7 @@
         <v>19.170000000000002</v>
       </c>
     </row>
-    <row r="537" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A537" s="1" t="s">
         <v>19</v>
       </c>
@@ -22977,7 +22989,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
         <v>19</v>
       </c>
@@ -23015,7 +23027,7 @@
         <v>19.170000000000002</v>
       </c>
     </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A539" s="1" t="s">
         <v>19</v>
       </c>
@@ -23053,7 +23065,7 @@
         <v>19.34</v>
       </c>
     </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
         <v>19</v>
       </c>
@@ -23091,7 +23103,7 @@
         <v>19.489999999999998</v>
       </c>
     </row>
-    <row r="541" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A541" s="1" t="s">
         <v>19</v>
       </c>
@@ -23129,7 +23141,7 @@
         <v>19.59</v>
       </c>
     </row>
-    <row r="542" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
         <v>19</v>
       </c>
@@ -23167,7 +23179,7 @@
         <v>19.64</v>
       </c>
     </row>
-    <row r="543" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A543" s="1" t="s">
         <v>19</v>
       </c>
@@ -23205,7 +23217,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="544" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
         <v>19</v>
       </c>
@@ -23243,7 +23255,7 @@
         <v>20.13</v>
       </c>
     </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A545" s="1" t="s">
         <v>19</v>
       </c>
@@ -23281,7 +23293,7 @@
         <v>19.96</v>
       </c>
     </row>
-    <row r="546" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
         <v>19</v>
       </c>
@@ -23319,7 +23331,7 @@
         <v>19.829999999999998</v>
       </c>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A547" s="1" t="s">
         <v>19</v>
       </c>
@@ -23357,7 +23369,7 @@
         <v>19.18</v>
       </c>
     </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
         <v>19</v>
       </c>
@@ -23395,7 +23407,7 @@
         <v>19.36</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A549" s="1" t="s">
         <v>19</v>
       </c>
@@ -23433,7 +23445,7 @@
         <v>19.78</v>
       </c>
     </row>
-    <row r="550" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
         <v>19</v>
       </c>
@@ -23471,7 +23483,7 @@
         <v>19.47</v>
       </c>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A551" s="1" t="s">
         <v>19</v>
       </c>
@@ -23509,7 +23521,7 @@
         <v>20.49</v>
       </c>
     </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
         <v>19</v>
       </c>
@@ -23547,7 +23559,7 @@
         <v>19.47</v>
       </c>
     </row>
-    <row r="553" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A553" s="1" t="s">
         <v>19</v>
       </c>
@@ -23585,7 +23597,7 @@
         <v>19.07</v>
       </c>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
         <v>19</v>
       </c>
@@ -23623,7 +23635,7 @@
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A555" s="1" t="s">
         <v>19</v>
       </c>
@@ -23661,7 +23673,7 @@
         <v>19.64</v>
       </c>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
         <v>19</v>
       </c>
@@ -23699,7 +23711,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A557" s="1" t="s">
         <v>19</v>
       </c>
@@ -23737,7 +23749,7 @@
         <v>19.809999999999999</v>
       </c>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
         <v>19</v>
       </c>
@@ -23775,7 +23787,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="559" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A559" s="1" t="s">
         <v>19</v>
       </c>
@@ -23813,7 +23825,7 @@
         <v>19.91</v>
       </c>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
         <v>19</v>
       </c>
@@ -23851,7 +23863,7 @@
         <v>18.45</v>
       </c>
     </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A561" s="1" t="s">
         <v>19</v>
       </c>
@@ -23889,7 +23901,7 @@
         <v>19.52</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
         <v>19</v>
       </c>
@@ -23927,7 +23939,7 @@
         <v>19.29</v>
       </c>
     </row>
-    <row r="563" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A563" s="1" t="s">
         <v>19</v>
       </c>
@@ -23965,7 +23977,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="564" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
         <v>19</v>
       </c>
@@ -24003,7 +24015,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="565" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A565" s="1" t="s">
         <v>19</v>
       </c>
@@ -24041,7 +24053,7 @@
         <v>19.510000000000002</v>
       </c>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
         <v>19</v>
       </c>
@@ -24079,7 +24091,7 @@
         <v>19.329999999999998</v>
       </c>
     </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A567" s="1" t="s">
         <v>19</v>
       </c>
@@ -24117,7 +24129,7 @@
         <v>18.399999999999999</v>
       </c>
     </row>
-    <row r="568" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
         <v>19</v>
       </c>
@@ -24155,7 +24167,7 @@
         <v>19.39</v>
       </c>
     </row>
-    <row r="569" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A569" s="1" t="s">
         <v>19</v>
       </c>
@@ -24193,7 +24205,7 @@
         <v>19.149999999999999</v>
       </c>
     </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
         <v>19</v>
       </c>
@@ -24231,7 +24243,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F571" s="1" t="s">
         <v>81</v>
       </c>
@@ -24251,7 +24263,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="572" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F572" s="1" t="s">
         <v>39</v>
       </c>
@@ -24271,7 +24283,7 @@
         <v>838.91999999999985</v>
       </c>
     </row>
-    <row r="573" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A573" s="1" t="s">
         <v>19</v>
       </c>
@@ -24309,7 +24321,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
         <v>19</v>
       </c>
@@ -24347,7 +24359,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="575" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A575" s="1" t="s">
         <v>19</v>
       </c>
@@ -24385,7 +24397,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="576" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
         <v>19</v>
       </c>
@@ -24423,7 +24435,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="577" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A577" s="1" t="s">
         <v>19</v>
       </c>
@@ -24461,7 +24473,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="578" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
         <v>19</v>
       </c>
@@ -24499,7 +24511,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="579" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A579" s="1" t="s">
         <v>19</v>
       </c>
@@ -24537,7 +24549,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="580" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
         <v>19</v>
       </c>
@@ -24575,7 +24587,7 @@
         <v>20.25</v>
       </c>
     </row>
-    <row r="581" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A581" s="1" t="s">
         <v>19</v>
       </c>
@@ -24613,7 +24625,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="582" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
         <v>19</v>
       </c>
@@ -24651,7 +24663,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="583" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A583" s="1" t="s">
         <v>19</v>
       </c>
@@ -24689,7 +24701,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="584" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
         <v>19</v>
       </c>
@@ -24727,7 +24739,7 @@
         <v>20.149999999999999</v>
       </c>
     </row>
-    <row r="585" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A585" s="1" t="s">
         <v>19</v>
       </c>
@@ -24765,7 +24777,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="586" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
         <v>19</v>
       </c>
@@ -24803,7 +24815,7 @@
         <v>19.95</v>
       </c>
     </row>
-    <row r="587" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A587" s="1" t="s">
         <v>19</v>
       </c>
@@ -24841,7 +24853,7 @@
         <v>19.899999999999999</v>
       </c>
     </row>
-    <row r="588" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
         <v>19</v>
       </c>
@@ -24879,7 +24891,7 @@
         <v>19.95</v>
       </c>
     </row>
-    <row r="589" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A589" s="1" t="s">
         <v>19</v>
       </c>
@@ -24917,7 +24929,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="590" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
         <v>19</v>
       </c>
@@ -24955,7 +24967,7 @@
         <v>20.25</v>
       </c>
     </row>
-    <row r="591" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A591" s="1" t="s">
         <v>19</v>
       </c>
@@ -24993,7 +25005,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="592" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
         <v>19</v>
       </c>
@@ -25031,7 +25043,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="593" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A593" s="1" t="s">
         <v>19</v>
       </c>
@@ -25069,7 +25081,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="594" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
         <v>19</v>
       </c>
@@ -25107,7 +25119,7 @@
         <v>20.100000000000001</v>
       </c>
     </row>
-    <row r="595" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A595" s="1" t="s">
         <v>19</v>
       </c>
@@ -25145,7 +25157,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="596" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F596" s="1" t="s">
         <v>81</v>
       </c>
@@ -25165,7 +25177,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="597" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F597" s="1" t="s">
         <v>837</v>
       </c>
@@ -25185,7 +25197,7 @@
         <v>457.25</v>
       </c>
     </row>
-    <row r="598" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F598" s="1" t="s">
         <v>81</v>
       </c>
@@ -25205,7 +25217,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="599" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A599" s="1" t="s">
         <v>838</v>
       </c>
@@ -25243,7 +25255,7 @@
         <v>27.15</v>
       </c>
     </row>
-    <row r="600" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F600" s="1" t="s">
         <v>81</v>
       </c>
@@ -25263,12 +25275,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="601" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K601" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="602" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="s">
         <v>838</v>
       </c>
@@ -25306,7 +25318,7 @@
         <v>55.4</v>
       </c>
     </row>
-    <row r="603" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F603" s="1" t="s">
         <v>81</v>
       </c>
@@ -25326,12 +25338,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="604" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:12" x14ac:dyDescent="0.3">
       <c r="K604" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="605" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A605" s="1" t="s">
         <v>838</v>
       </c>
@@ -25369,7 +25381,7 @@
         <v>192.25</v>
       </c>
     </row>
-    <row r="606" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F606" s="1" t="s">
         <v>81</v>
       </c>
@@ -25389,7 +25401,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="608" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A608" s="1" t="s">
         <v>838</v>
       </c>
@@ -25427,7 +25439,7 @@
         <v>78.45</v>
       </c>
     </row>
-    <row r="609" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F609" s="1" t="s">
         <v>81</v>
       </c>
@@ -25447,7 +25459,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="611" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A611" s="1" t="s">
         <v>838</v>
       </c>
@@ -25485,7 +25497,7 @@
         <v>321.10000000000002</v>
       </c>
     </row>
-    <row r="612" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F612" s="1" t="s">
         <v>81</v>
       </c>
@@ -25505,7 +25517,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="614" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A614" s="1" t="s">
         <v>838</v>
       </c>
@@ -25543,7 +25555,7 @@
         <v>53.42</v>
       </c>
     </row>
-    <row r="615" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F615" s="1" t="s">
         <v>81</v>
       </c>
@@ -25563,7 +25575,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="617" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A617" s="1" t="s">
         <v>838</v>
       </c>
@@ -25601,7 +25613,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="618" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:12" x14ac:dyDescent="0.3">
       <c r="F618" s="1" t="s">
         <v>81</v>
       </c>
@@ -25625,4 +25637,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57862396-7B88-4576-A249-1D2CB900AC6F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>47328</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>